--- a/Structure_Data/text.9.14/20260914_139/structure_factor_20260914_139.xlsx
+++ b/Structure_Data/text.9.14/20260914_139/structure_factor_20260914_139.xlsx
@@ -40,7 +40,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B20"/>
+  <dimension ref="A1:D394"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -248,6 +248,4194 @@
         <v>18.860229117468</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度 beta / Constrictivity (x)</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈半径 r_min (um)</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">孔体半径 r_max (um)</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">瓶颈度状态 / Constrictivity Status</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">侵入入口 / Intrusion Inlet</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">low</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球心邻域 / Center Connectivity</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">算法版本 / Method</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">edt_critical_radii_closed_dilation_v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">半径采样 / Radius Sampling</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">All positive EDT values</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius (um)</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CPSD (total volume fraction)</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">MIP (total volume fraction)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30">
+        <v>0</v>
+      </c>
+      <c r="B30">
+        <v>0.326263427734375</v>
+      </c>
+      <c r="C30">
+        <v>0.325740814208984</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31">
+        <v>0.5</v>
+      </c>
+      <c r="B31">
+        <v>0.326263427734375</v>
+      </c>
+      <c r="C31">
+        <v>0.325740814208984</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B32">
+        <v>0.292076110839844</v>
+      </c>
+      <c r="C32">
+        <v>0.283557891845703</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B33">
+        <v>0.230266571044922</v>
+      </c>
+      <c r="C33">
+        <v>0.201103210449219</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34">
+        <v>1</v>
+      </c>
+      <c r="B34">
+        <v>0.2071533203125</v>
+      </c>
+      <c r="C34">
+        <v>0.134670257568359</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B35">
+        <v>0.192481994628906</v>
+      </c>
+      <c r="C35">
+        <v>0.0499839782714844</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B36">
+        <v>0.135379791259766</v>
+      </c>
+      <c r="C36">
+        <v>0.0273628234863281</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B37">
+        <v>0.109539031982422</v>
+      </c>
+      <c r="C37">
+        <v>0.0194892883300781</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38">
+        <v>1.5</v>
+      </c>
+      <c r="B38">
+        <v>0.0931777954101562</v>
+      </c>
+      <c r="C38">
+        <v>0.0159187316894531</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B39">
+        <v>0.060699462890625</v>
+      </c>
+      <c r="C39">
+        <v>0.00992202758789062</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B40">
+        <v>0.0501289367675781</v>
+      </c>
+      <c r="C40">
+        <v>0.00938034057617188</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B41">
+        <v>0.0397071838378906</v>
+      </c>
+      <c r="C41">
+        <v>0.0083465576171875</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B42">
+        <v>0.0389633178710938</v>
+      </c>
+      <c r="C42">
+        <v>0.00856399536132812</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B43">
+        <v>0.0312538146972656</v>
+      </c>
+      <c r="C43">
+        <v>0.00827789306640625</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44">
+        <v>2</v>
+      </c>
+      <c r="B44">
+        <v>0.0223884582519531</v>
+      </c>
+      <c r="C44">
+        <v>0.005615234375</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B45">
+        <v>0.0217628479003906</v>
+      </c>
+      <c r="C45">
+        <v>0.00612640380859375</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B46">
+        <v>0.0135498046875</v>
+      </c>
+      <c r="C46">
+        <v>0.00499343872070312</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B47">
+        <v>0.00771331787109375</v>
+      </c>
+      <c r="C47">
+        <v>0.00265884399414062</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B48">
+        <v>0.0078277587890625</v>
+      </c>
+      <c r="C48">
+        <v>0.00254058837890625</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B49">
+        <v>0.00750350952148438</v>
+      </c>
+      <c r="C49">
+        <v>0.00116729736328125</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B50">
+        <v>0.00307464599609375</v>
+      </c>
+      <c r="C50">
+        <v>0.00100326538085938</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51">
+        <v>2.5</v>
+      </c>
+      <c r="B51">
+        <v>0.00195693969726562</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52">
+        <v>3</v>
+      </c>
+      <c r="B52">
+        <v>0</v>
+      </c>
+      <c r="C52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53"/>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">弦长分布 / Chord Length</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_voxel_runs_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>18197</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>2.35005770181898</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>2.17314781757197</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Axis</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Window-spanning lines</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full pore line policy</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">one_period_censored</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>0.05</v>
+      </c>
+      <c r="B68">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>0.1</v>
+      </c>
+      <c r="B69">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>0.15</v>
+      </c>
+      <c r="B70">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>0.2</v>
+      </c>
+      <c r="B71">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>0.25</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>0.3</v>
+      </c>
+      <c r="B73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>0.35</v>
+      </c>
+      <c r="B74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>0.4</v>
+      </c>
+      <c r="B75">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>0.45</v>
+      </c>
+      <c r="B76">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>0.5</v>
+      </c>
+      <c r="B77">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>0.55</v>
+      </c>
+      <c r="B78">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>0.6</v>
+      </c>
+      <c r="B79">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>0.65</v>
+      </c>
+      <c r="B80">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>0.7</v>
+      </c>
+      <c r="B81">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>0.75</v>
+      </c>
+      <c r="B82">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>0.8</v>
+      </c>
+      <c r="B83">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>0.85</v>
+      </c>
+      <c r="B84">
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>0.9</v>
+      </c>
+      <c r="B85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>0.95</v>
+      </c>
+      <c r="B86">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>0.5</v>
+      </c>
+      <c r="B88">
+        <v>4296</v>
+      </c>
+      <c r="C88">
+        <v>0.23608287080288</v>
+      </c>
+      <c r="D88">
+        <v>0.23608287080288</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>1</v>
+      </c>
+      <c r="B89">
+        <v>3039</v>
+      </c>
+      <c r="C89">
+        <v>0.167005550365445</v>
+      </c>
+      <c r="D89">
+        <v>0.403088421168324</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>1.5</v>
+      </c>
+      <c r="B90">
+        <v>2262</v>
+      </c>
+      <c r="C90">
+        <v>0.124306204319393</v>
+      </c>
+      <c r="D90">
+        <v>0.527394625487718</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>2</v>
+      </c>
+      <c r="B91">
+        <v>1745</v>
+      </c>
+      <c r="C91">
+        <v>0.095894927735341</v>
+      </c>
+      <c r="D91">
+        <v>0.623289553223059</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>2.5</v>
+      </c>
+      <c r="B92">
+        <v>1385</v>
+      </c>
+      <c r="C92">
+        <v>0.0761114469418036</v>
+      </c>
+      <c r="D92">
+        <v>0.699401000164862</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>3</v>
+      </c>
+      <c r="B93">
+        <v>1083</v>
+      </c>
+      <c r="C93">
+        <v>0.0595153047205583</v>
+      </c>
+      <c r="D93">
+        <v>0.758916304885421</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>3.5</v>
+      </c>
+      <c r="B94">
+        <v>852</v>
+      </c>
+      <c r="C94">
+        <v>0.0468209045447052</v>
+      </c>
+      <c r="D94">
+        <v>0.805737209430126</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>4</v>
+      </c>
+      <c r="B95">
+        <v>671</v>
+      </c>
+      <c r="C95">
+        <v>0.0368742100346211</v>
+      </c>
+      <c r="D95">
+        <v>0.842611419464747</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>4.5</v>
+      </c>
+      <c r="B96">
+        <v>629</v>
+      </c>
+      <c r="C96">
+        <v>0.0345661372753751</v>
+      </c>
+      <c r="D96">
+        <v>0.877177556740122</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>5</v>
+      </c>
+      <c r="B97">
+        <v>485</v>
+      </c>
+      <c r="C97">
+        <v>0.0266527449579601</v>
+      </c>
+      <c r="D97">
+        <v>0.903830301698082</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>5.5</v>
+      </c>
+      <c r="B98">
+        <v>349</v>
+      </c>
+      <c r="C98">
+        <v>0.0191789855470682</v>
+      </c>
+      <c r="D98">
+        <v>0.92300928724515</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>6</v>
+      </c>
+      <c r="B99">
+        <v>317</v>
+      </c>
+      <c r="C99">
+        <v>0.017420453920976</v>
+      </c>
+      <c r="D99">
+        <v>0.940429741166126</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>6.5</v>
+      </c>
+      <c r="B100">
+        <v>209</v>
+      </c>
+      <c r="C100">
+        <v>0.0114854096829148</v>
+      </c>
+      <c r="D100">
+        <v>0.951915150849041</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>7</v>
+      </c>
+      <c r="B101">
+        <v>164</v>
+      </c>
+      <c r="C101">
+        <v>0.00901247458372259</v>
+      </c>
+      <c r="D101">
+        <v>0.960927625432764</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>7.5</v>
+      </c>
+      <c r="B102">
+        <v>128</v>
+      </c>
+      <c r="C102">
+        <v>0.00703412650436885</v>
+      </c>
+      <c r="D102">
+        <v>0.967961751937133</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>8</v>
+      </c>
+      <c r="B103">
+        <v>132</v>
+      </c>
+      <c r="C103">
+        <v>0.00725394295763038</v>
+      </c>
+      <c r="D103">
+        <v>0.975215694894763</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>8.5</v>
+      </c>
+      <c r="B104">
+        <v>81</v>
+      </c>
+      <c r="C104">
+        <v>0.00445128317854591</v>
+      </c>
+      <c r="D104">
+        <v>0.979666978073309</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>9</v>
+      </c>
+      <c r="B105">
+        <v>73</v>
+      </c>
+      <c r="C105">
+        <v>0.00401165027202286</v>
+      </c>
+      <c r="D105">
+        <v>0.983678628345332</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>9.5</v>
+      </c>
+      <c r="B106">
+        <v>53</v>
+      </c>
+      <c r="C106">
+        <v>0.00291256800571523</v>
+      </c>
+      <c r="D106">
+        <v>0.986591196351047</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>10</v>
+      </c>
+      <c r="B107">
+        <v>44</v>
+      </c>
+      <c r="C107">
+        <v>0.00241798098587679</v>
+      </c>
+      <c r="D107">
+        <v>0.989009177336924</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>10.5</v>
+      </c>
+      <c r="B108">
+        <v>63</v>
+      </c>
+      <c r="C108">
+        <v>0.00346210913886904</v>
+      </c>
+      <c r="D108">
+        <v>0.992471286475793</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>11</v>
+      </c>
+      <c r="B109">
+        <v>35</v>
+      </c>
+      <c r="C109">
+        <v>0.00192339396603836</v>
+      </c>
+      <c r="D109">
+        <v>0.994394680441831</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>11.5</v>
+      </c>
+      <c r="B110">
+        <v>18</v>
+      </c>
+      <c r="C110">
+        <v>0.00098917403967687</v>
+      </c>
+      <c r="D110">
+        <v>0.995383854481508</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>12</v>
+      </c>
+      <c r="B111">
+        <v>15</v>
+      </c>
+      <c r="C111">
+        <v>0.000824311699730725</v>
+      </c>
+      <c r="D111">
+        <v>0.996208166181239</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>12.5</v>
+      </c>
+      <c r="B112">
+        <v>15</v>
+      </c>
+      <c r="C112">
+        <v>0.000824311699730725</v>
+      </c>
+      <c r="D112">
+        <v>0.997032477880969</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>13</v>
+      </c>
+      <c r="B113">
+        <v>15</v>
+      </c>
+      <c r="C113">
+        <v>0.000824311699730725</v>
+      </c>
+      <c r="D113">
+        <v>0.9978567895807</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>13.5</v>
+      </c>
+      <c r="B114">
+        <v>11</v>
+      </c>
+      <c r="C114">
+        <v>0.000604495246469198</v>
+      </c>
+      <c r="D114">
+        <v>0.998461284827169</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>14</v>
+      </c>
+      <c r="B115">
+        <v>5</v>
+      </c>
+      <c r="C115">
+        <v>0.000274770566576908</v>
+      </c>
+      <c r="D115">
+        <v>0.998736055393746</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>14.5</v>
+      </c>
+      <c r="B116">
+        <v>3</v>
+      </c>
+      <c r="C116">
+        <v>0.000164862339946145</v>
+      </c>
+      <c r="D116">
+        <v>0.998900917733692</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>15</v>
+      </c>
+      <c r="B117">
+        <v>1</v>
+      </c>
+      <c r="C117">
+        <v>5.49541133153817e-05</v>
+      </c>
+      <c r="D117">
+        <v>0.998955871847008</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>16</v>
+      </c>
+      <c r="B118">
+        <v>3</v>
+      </c>
+      <c r="C118">
+        <v>0.000164862339946145</v>
+      </c>
+      <c r="D118">
+        <v>0.999120734186954</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>16.5</v>
+      </c>
+      <c r="B119">
+        <v>2</v>
+      </c>
+      <c r="C119">
+        <v>0.000109908226630763</v>
+      </c>
+      <c r="D119">
+        <v>0.999230642413585</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>17</v>
+      </c>
+      <c r="B120">
+        <v>4</v>
+      </c>
+      <c r="C120">
+        <v>0.000219816453261527</v>
+      </c>
+      <c r="D120">
+        <v>0.999450458866846</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>17.5</v>
+      </c>
+      <c r="B121">
+        <v>2</v>
+      </c>
+      <c r="C121">
+        <v>0.000109908226630763</v>
+      </c>
+      <c r="D121">
+        <v>0.999560367093477</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>18</v>
+      </c>
+      <c r="B122">
+        <v>3</v>
+      </c>
+      <c r="C122">
+        <v>0.000164862339946145</v>
+      </c>
+      <c r="D122">
+        <v>0.999725229433423</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>18.5</v>
+      </c>
+      <c r="B123">
+        <v>2</v>
+      </c>
+      <c r="C123">
+        <v>0.000109908226630763</v>
+      </c>
+      <c r="D123">
+        <v>0.999835137660054</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>19</v>
+      </c>
+      <c r="B124">
+        <v>1</v>
+      </c>
+      <c r="C124">
+        <v>5.49541133153817e-05</v>
+      </c>
+      <c r="D124">
+        <v>0.999890091773369</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>19.5</v>
+      </c>
+      <c r="B125">
+        <v>1</v>
+      </c>
+      <c r="C125">
+        <v>5.49541133153817e-05</v>
+      </c>
+      <c r="D125">
+        <v>0.999945045886685</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>21.5</v>
+      </c>
+      <c r="B126">
+        <v>1</v>
+      </c>
+      <c r="C126">
+        <v>5.49541133153817e-05</v>
+      </c>
+      <c r="D126">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127"/>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">球接触分布 / Spherical Contact</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_solid_to_pore_edt_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sample count</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>176616</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean (um)</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>0.915952278033245</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Population std (um)</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>0.444029356440409</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile method</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">inverse_empirical_cdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance direction</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">solid_to_pore</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Distance convention</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">voxel_center_to_voxel_center</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Quantile</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>0.05</v>
+      </c>
+      <c r="B141">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>0.1</v>
+      </c>
+      <c r="B142">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>0.15</v>
+      </c>
+      <c r="B143">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>0.2</v>
+      </c>
+      <c r="B144">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>0.25</v>
+      </c>
+      <c r="B145">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>0.3</v>
+      </c>
+      <c r="B146">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>0.35</v>
+      </c>
+      <c r="B147">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>0.4</v>
+      </c>
+      <c r="B148">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>0.45</v>
+      </c>
+      <c r="B149">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>0.5</v>
+      </c>
+      <c r="B150">
+        <v>0.707106781186548</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151">
+        <v>0.55</v>
+      </c>
+      <c r="B151">
+        <v>0.866025403784439</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152">
+        <v>0.6</v>
+      </c>
+      <c r="B152">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153">
+        <v>0.65</v>
+      </c>
+      <c r="B153">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154">
+        <v>0.7</v>
+      </c>
+      <c r="B154">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155">
+        <v>0.75</v>
+      </c>
+      <c r="B155">
+        <v>1.11803398874989</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156">
+        <v>0.8</v>
+      </c>
+      <c r="B156">
+        <v>1.22474487139159</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157">
+        <v>0.85</v>
+      </c>
+      <c r="B157">
+        <v>1.4142135623731</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158">
+        <v>0.9</v>
+      </c>
+      <c r="B158">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159">
+        <v>0.95</v>
+      </c>
+      <c r="B159">
+        <v>1.73205080756888</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Length (um)</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Count</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Probability mass</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161">
+        <v>0.5</v>
+      </c>
+      <c r="B161">
+        <v>57781</v>
+      </c>
+      <c r="C161">
+        <v>0.327156090048467</v>
+      </c>
+      <c r="D161">
+        <v>0.327156090048467</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162">
+        <v>0.707106781186548</v>
+      </c>
+      <c r="B162">
+        <v>31913</v>
+      </c>
+      <c r="C162">
+        <v>0.18069144358382</v>
+      </c>
+      <c r="D162">
+        <v>0.507847533632287</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163">
+        <v>0.866025403784439</v>
+      </c>
+      <c r="B163">
+        <v>14183</v>
+      </c>
+      <c r="C163">
+        <v>0.0803041627032658</v>
+      </c>
+      <c r="D163">
+        <v>0.588151696335553</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164">
+        <v>1</v>
+      </c>
+      <c r="B164">
+        <v>11430</v>
+      </c>
+      <c r="C164">
+        <v>0.0647166734610681</v>
+      </c>
+      <c r="D164">
+        <v>0.652868369796621</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165">
+        <v>1.11803398874989</v>
+      </c>
+      <c r="B165">
+        <v>20712</v>
+      </c>
+      <c r="C165">
+        <v>0.117271368392445</v>
+      </c>
+      <c r="D165">
+        <v>0.770139738189066</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166">
+        <v>1.22474487139159</v>
+      </c>
+      <c r="B166">
+        <v>9931</v>
+      </c>
+      <c r="C166">
+        <v>0.0562293336957014</v>
+      </c>
+      <c r="D166">
+        <v>0.826369071884767</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167">
+        <v>1.4142135623731</v>
+      </c>
+      <c r="B167">
+        <v>7552</v>
+      </c>
+      <c r="C167">
+        <v>0.042759432893962</v>
+      </c>
+      <c r="D167">
+        <v>0.869128504778729</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168">
+        <v>1.5</v>
+      </c>
+      <c r="B168">
+        <v>8181</v>
+      </c>
+      <c r="C168">
+        <v>0.046320831634733</v>
+      </c>
+      <c r="D168">
+        <v>0.915449336413462</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169">
+        <v>1.58113883008419</v>
+      </c>
+      <c r="B169">
+        <v>3202</v>
+      </c>
+      <c r="C169">
+        <v>0.0181297277709834</v>
+      </c>
+      <c r="D169">
+        <v>0.933579064184445</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170">
+        <v>1.6583123951777</v>
+      </c>
+      <c r="B170">
+        <v>2607</v>
+      </c>
+      <c r="C170">
+        <v>0.0147608370702541</v>
+      </c>
+      <c r="D170">
+        <v>0.948339901254699</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171">
+        <v>1.73205080756888</v>
+      </c>
+      <c r="B171">
+        <v>951</v>
+      </c>
+      <c r="C171">
+        <v>0.00538456311998913</v>
+      </c>
+      <c r="D171">
+        <v>0.953724464374689</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172">
+        <v>1.80277563773199</v>
+      </c>
+      <c r="B172">
+        <v>2145</v>
+      </c>
+      <c r="C172">
+        <v>0.0121449925261584</v>
+      </c>
+      <c r="D172">
+        <v>0.965869456900847</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173">
+        <v>1.87082869338697</v>
+      </c>
+      <c r="B173">
+        <v>1934</v>
+      </c>
+      <c r="C173">
+        <v>0.0109503102776645</v>
+      </c>
+      <c r="D173">
+        <v>0.976819767178512</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174">
+        <v>2</v>
+      </c>
+      <c r="B174">
+        <v>358</v>
+      </c>
+      <c r="C174">
+        <v>0.00202699642161526</v>
+      </c>
+      <c r="D174">
+        <v>0.978846763600127</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175">
+        <v>2.06155281280883</v>
+      </c>
+      <c r="B175">
+        <v>1218</v>
+      </c>
+      <c r="C175">
+        <v>0.00689631743443403</v>
+      </c>
+      <c r="D175">
+        <v>0.985743081034561</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176">
+        <v>2.12132034355964</v>
+      </c>
+      <c r="B176">
+        <v>403</v>
+      </c>
+      <c r="C176">
+        <v>0.00228178647461159</v>
+      </c>
+      <c r="D176">
+        <v>0.988024867509172</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177">
+        <v>2.17944947177034</v>
+      </c>
+      <c r="B177">
+        <v>222</v>
+      </c>
+      <c r="C177">
+        <v>0.00125696426144857</v>
+      </c>
+      <c r="D177">
+        <v>0.989281831770621</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178">
+        <v>2.23606797749979</v>
+      </c>
+      <c r="B178">
+        <v>174</v>
+      </c>
+      <c r="C178">
+        <v>0.000985188204919147</v>
+      </c>
+      <c r="D178">
+        <v>0.99026701997554</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179">
+        <v>2.29128784747792</v>
+      </c>
+      <c r="B179">
+        <v>226</v>
+      </c>
+      <c r="C179">
+        <v>0.00127961226615935</v>
+      </c>
+      <c r="D179">
+        <v>0.991546632241699</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180">
+        <v>2.34520787991171</v>
+      </c>
+      <c r="B180">
+        <v>97</v>
+      </c>
+      <c r="C180">
+        <v>0.000549214114236536</v>
+      </c>
+      <c r="D180">
+        <v>0.992095846355936</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181">
+        <v>2.44948974278318</v>
+      </c>
+      <c r="B181">
+        <v>102</v>
+      </c>
+      <c r="C181">
+        <v>0.000577524120125017</v>
+      </c>
+      <c r="D181">
+        <v>0.992673370476061</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182">
+        <v>2.5</v>
+      </c>
+      <c r="B182">
+        <v>99</v>
+      </c>
+      <c r="C182">
+        <v>0.000560538116591928</v>
+      </c>
+      <c r="D182">
+        <v>0.993233908592653</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183">
+        <v>2.54950975679639</v>
+      </c>
+      <c r="B183">
+        <v>189</v>
+      </c>
+      <c r="C183">
+        <v>0.00107011822258459</v>
+      </c>
+      <c r="D183">
+        <v>0.994304026815238</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184">
+        <v>2.59807621135332</v>
+      </c>
+      <c r="B184">
+        <v>74</v>
+      </c>
+      <c r="C184">
+        <v>0.000418988087149522</v>
+      </c>
+      <c r="D184">
+        <v>0.994723014902387</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185">
+        <v>2.69258240356725</v>
+      </c>
+      <c r="B185">
+        <v>145</v>
+      </c>
+      <c r="C185">
+        <v>0.000820990170765955</v>
+      </c>
+      <c r="D185">
+        <v>0.995544005073153</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186">
+        <v>2.73861278752583</v>
+      </c>
+      <c r="B186">
+        <v>66</v>
+      </c>
+      <c r="C186">
+        <v>0.000373692077727952</v>
+      </c>
+      <c r="D186">
+        <v>0.995917697150881</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187">
+        <v>2.82842712474619</v>
+      </c>
+      <c r="B187">
+        <v>18</v>
+      </c>
+      <c r="C187">
+        <v>0.000101916021198532</v>
+      </c>
+      <c r="D187">
+        <v>0.99601961317208</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188">
+        <v>2.87228132326901</v>
+      </c>
+      <c r="B188">
+        <v>63</v>
+      </c>
+      <c r="C188">
+        <v>0.000356706074194863</v>
+      </c>
+      <c r="D188">
+        <v>0.996376319246274</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189">
+        <v>2.91547594742265</v>
+      </c>
+      <c r="B189">
+        <v>63</v>
+      </c>
+      <c r="C189">
+        <v>0.000356706074194863</v>
+      </c>
+      <c r="D189">
+        <v>0.996733025320469</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190">
+        <v>2.95803989154981</v>
+      </c>
+      <c r="B190">
+        <v>51</v>
+      </c>
+      <c r="C190">
+        <v>0.000288762060062508</v>
+      </c>
+      <c r="D190">
+        <v>0.997021787380532</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191">
+        <v>3</v>
+      </c>
+      <c r="B191">
+        <v>28</v>
+      </c>
+      <c r="C191">
+        <v>0.000158536032975495</v>
+      </c>
+      <c r="D191">
+        <v>0.997180323413507</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192">
+        <v>3.04138126514911</v>
+      </c>
+      <c r="B192">
+        <v>21</v>
+      </c>
+      <c r="C192">
+        <v>0.000118902024731621</v>
+      </c>
+      <c r="D192">
+        <v>0.997299225438239</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193">
+        <v>3.08220700148449</v>
+      </c>
+      <c r="B193">
+        <v>61</v>
+      </c>
+      <c r="C193">
+        <v>0.000345382071839471</v>
+      </c>
+      <c r="D193">
+        <v>0.997644607510078</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194">
+        <v>3.16227766016838</v>
+      </c>
+      <c r="B194">
+        <v>20</v>
+      </c>
+      <c r="C194">
+        <v>0.000113240023553925</v>
+      </c>
+      <c r="D194">
+        <v>0.997757847533632</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195">
+        <v>3.20156211871642</v>
+      </c>
+      <c r="B195">
+        <v>73</v>
+      </c>
+      <c r="C195">
+        <v>0.000413326085971826</v>
+      </c>
+      <c r="D195">
+        <v>0.998171173619604</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196">
+        <v>3.24037034920393</v>
+      </c>
+      <c r="B196">
+        <v>22</v>
+      </c>
+      <c r="C196">
+        <v>0.000124564025909317</v>
+      </c>
+      <c r="D196">
+        <v>0.998295737645513</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197">
+        <v>3.278719262151</v>
+      </c>
+      <c r="B197">
+        <v>13</v>
+      </c>
+      <c r="C197">
+        <v>7.36060153100512e-05</v>
+      </c>
+      <c r="D197">
+        <v>0.998369343660824</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198">
+        <v>3.3166247903554</v>
+      </c>
+      <c r="B198">
+        <v>12</v>
+      </c>
+      <c r="C198">
+        <v>6.79440141323549e-05</v>
+      </c>
+      <c r="D198">
+        <v>0.998437287674956</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199">
+        <v>3.35410196624968</v>
+      </c>
+      <c r="B199">
+        <v>34</v>
+      </c>
+      <c r="C199">
+        <v>0.000192508040041672</v>
+      </c>
+      <c r="D199">
+        <v>0.998629795714998</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200">
+        <v>3.39116499156263</v>
+      </c>
+      <c r="B200">
+        <v>17</v>
+      </c>
+      <c r="C200">
+        <v>9.62540200208362e-05</v>
+      </c>
+      <c r="D200">
+        <v>0.998726049735018</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201">
+        <v>3.46410161513775</v>
+      </c>
+      <c r="B201">
+        <v>10</v>
+      </c>
+      <c r="C201">
+        <v>5.66200117769625e-05</v>
+      </c>
+      <c r="D201">
+        <v>0.998782669746795</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202">
+        <v>3.5</v>
+      </c>
+      <c r="B202">
+        <v>20</v>
+      </c>
+      <c r="C202">
+        <v>0.000113240023553925</v>
+      </c>
+      <c r="D202">
+        <v>0.998895909770349</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203">
+        <v>3.53553390593274</v>
+      </c>
+      <c r="B203">
+        <v>34</v>
+      </c>
+      <c r="C203">
+        <v>0.000192508040041672</v>
+      </c>
+      <c r="D203">
+        <v>0.999088417810391</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204">
+        <v>3.57071421427143</v>
+      </c>
+      <c r="B204">
+        <v>13</v>
+      </c>
+      <c r="C204">
+        <v>7.36060153100512e-05</v>
+      </c>
+      <c r="D204">
+        <v>0.999162023825701</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205">
+        <v>3.60555127546399</v>
+      </c>
+      <c r="B205">
+        <v>6</v>
+      </c>
+      <c r="C205">
+        <v>3.39720070661775e-05</v>
+      </c>
+      <c r="D205">
+        <v>0.999195995832767</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206">
+        <v>3.64005494464026</v>
+      </c>
+      <c r="B206">
+        <v>15</v>
+      </c>
+      <c r="C206">
+        <v>8.49300176654437e-05</v>
+      </c>
+      <c r="D206">
+        <v>0.999280925850433</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207">
+        <v>3.67423461417477</v>
+      </c>
+      <c r="B207">
+        <v>24</v>
+      </c>
+      <c r="C207">
+        <v>0.00013588802826471</v>
+      </c>
+      <c r="D207">
+        <v>0.999416813878697</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208">
+        <v>3.74165738677394</v>
+      </c>
+      <c r="B208">
+        <v>10</v>
+      </c>
+      <c r="C208">
+        <v>5.66200117769625e-05</v>
+      </c>
+      <c r="D208">
+        <v>0.999473433890474</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209">
+        <v>3.77491721763537</v>
+      </c>
+      <c r="B209">
+        <v>11</v>
+      </c>
+      <c r="C209">
+        <v>6.22820129546587e-05</v>
+      </c>
+      <c r="D209">
+        <v>0.999535715903429</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210">
+        <v>3.80788655293195</v>
+      </c>
+      <c r="B210">
+        <v>4</v>
+      </c>
+      <c r="C210">
+        <v>2.2648004710785e-05</v>
+      </c>
+      <c r="D210">
+        <v>0.99955836390814</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211">
+        <v>3.8405728739343</v>
+      </c>
+      <c r="B211">
+        <v>14</v>
+      </c>
+      <c r="C211">
+        <v>7.92680164877474e-05</v>
+      </c>
+      <c r="D211">
+        <v>0.999637631924627</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212">
+        <v>3.90512483795333</v>
+      </c>
+      <c r="B212">
+        <v>10</v>
+      </c>
+      <c r="C212">
+        <v>5.66200117769625e-05</v>
+      </c>
+      <c r="D212">
+        <v>0.999694251936404</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213">
+        <v>3.93700393700591</v>
+      </c>
+      <c r="B213">
+        <v>7</v>
+      </c>
+      <c r="C213">
+        <v>3.96340082438737e-05</v>
+      </c>
+      <c r="D213">
+        <v>0.999733885944648</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214">
+        <v>4.03112887414927</v>
+      </c>
+      <c r="B214">
+        <v>8</v>
+      </c>
+      <c r="C214">
+        <v>4.529600942157e-05</v>
+      </c>
+      <c r="D214">
+        <v>0.99977918195407</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215">
+        <v>4.06201920231798</v>
+      </c>
+      <c r="B215">
+        <v>11</v>
+      </c>
+      <c r="C215">
+        <v>6.22820129546587e-05</v>
+      </c>
+      <c r="D215">
+        <v>0.999841463967025</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216">
+        <v>4.12310562561766</v>
+      </c>
+      <c r="B216">
+        <v>6</v>
+      </c>
+      <c r="C216">
+        <v>3.39720070661775e-05</v>
+      </c>
+      <c r="D216">
+        <v>0.999875435974091</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217">
+        <v>4.15331193145904</v>
+      </c>
+      <c r="B217">
+        <v>6</v>
+      </c>
+      <c r="C217">
+        <v>3.39720070661775e-05</v>
+      </c>
+      <c r="D217">
+        <v>0.999909407981157</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218">
+        <v>4.18330013267038</v>
+      </c>
+      <c r="B218">
+        <v>3</v>
+      </c>
+      <c r="C218">
+        <v>1.69860035330887e-05</v>
+      </c>
+      <c r="D218">
+        <v>0.99992639398469</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219">
+        <v>4.24264068711928</v>
+      </c>
+      <c r="B219">
+        <v>3</v>
+      </c>
+      <c r="C219">
+        <v>1.69860035330887e-05</v>
+      </c>
+      <c r="D219">
+        <v>0.999943379988223</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220">
+        <v>4.27200187265877</v>
+      </c>
+      <c r="B220">
+        <v>1</v>
+      </c>
+      <c r="C220">
+        <v>5.66200117769624e-06</v>
+      </c>
+      <c r="D220">
+        <v>0.999949041989401</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221">
+        <v>4.30116263352131</v>
+      </c>
+      <c r="B221">
+        <v>4</v>
+      </c>
+      <c r="C221">
+        <v>2.2648004710785e-05</v>
+      </c>
+      <c r="D221">
+        <v>0.999971689994112</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222">
+        <v>4.35889894354067</v>
+      </c>
+      <c r="B222">
+        <v>2</v>
+      </c>
+      <c r="C222">
+        <v>1.13240023553925e-05</v>
+      </c>
+      <c r="D222">
+        <v>0.999983013996467</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223">
+        <v>4.38748219369606</v>
+      </c>
+      <c r="B223">
+        <v>2</v>
+      </c>
+      <c r="C223">
+        <v>1.13240023553925e-05</v>
+      </c>
+      <c r="D223">
+        <v>0.999994337998822</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224">
+        <v>4.5</v>
+      </c>
+      <c r="B224">
+        <v>1</v>
+      </c>
+      <c r="C224">
+        <v>5.66200117769624e-06</v>
+      </c>
+      <c r="D224">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="225"/>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">两点相关函数 / Two-Point Correlation</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Status</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ok</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Method</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">periodic_fft_radial_shells_v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore label</t>
+        </is>
+      </c>
+      <c r="B229">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Porosity</t>
+        </is>
+      </c>
+      <c r="B230">
+        <v>0.326263427734375</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voxel size (um)</t>
+        </is>
+      </c>
+      <c r="B231">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Periodic axes</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">xyz</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radial bins</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">bin_0_origin_only; bin_k: (k-1)*h &lt; distance &lt;= k*h</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normalization</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">joint_probability; C(0)=porosity</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Radius upper edge (um)</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Displacement count</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mean distance (um)</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236">
+        <v>0</v>
+      </c>
+      <c r="B236">
+        <v>0.326263427734375</v>
+      </c>
+      <c r="C236">
+        <v>1</v>
+      </c>
+      <c r="D236">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237">
+        <v>0.5</v>
+      </c>
+      <c r="B237">
+        <v>0.259302775065104</v>
+      </c>
+      <c r="C237">
+        <v>6</v>
+      </c>
+      <c r="D237">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238">
+        <v>1</v>
+      </c>
+      <c r="B238">
+        <v>0.226218003493089</v>
+      </c>
+      <c r="C238">
+        <v>26</v>
+      </c>
+      <c r="D238">
+        <v>0.82359556171208</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239">
+        <v>1.5</v>
+      </c>
+      <c r="B239">
+        <v>0.186744181315104</v>
+      </c>
+      <c r="C239">
+        <v>90</v>
+      </c>
+      <c r="D239">
+        <v>1.31330283768748</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240">
+        <v>2</v>
+      </c>
+      <c r="B240">
+        <v>0.159504733868499</v>
+      </c>
+      <c r="C240">
+        <v>134</v>
+      </c>
+      <c r="D240">
+        <v>1.76619125712671</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241">
+        <v>2.5</v>
+      </c>
+      <c r="B241">
+        <v>0.13915462641753</v>
+      </c>
+      <c r="C241">
+        <v>258</v>
+      </c>
+      <c r="D241">
+        <v>2.25329087515144</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242">
+        <v>3</v>
+      </c>
+      <c r="B242">
+        <v>0.125340717594798</v>
+      </c>
+      <c r="C242">
+        <v>410</v>
+      </c>
+      <c r="D242">
+        <v>2.77015092047628</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243">
+        <v>3.5</v>
+      </c>
+      <c r="B243">
+        <v>0.117849774688844</v>
+      </c>
+      <c r="C243">
+        <v>494</v>
+      </c>
+      <c r="D243">
+        <v>3.26511495914839</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244">
+        <v>4</v>
+      </c>
+      <c r="B244">
+        <v>0.114627451136492</v>
+      </c>
+      <c r="C244">
+        <v>690</v>
+      </c>
+      <c r="D244">
+        <v>3.74137726298534</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245">
+        <v>4.5</v>
+      </c>
+      <c r="B245">
+        <v>0.113437803272398</v>
+      </c>
+      <c r="C245">
+        <v>962</v>
+      </c>
+      <c r="D245">
+        <v>4.25479734207796</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246">
+        <v>5</v>
+      </c>
+      <c r="B246">
+        <v>0.112989727916613</v>
+      </c>
+      <c r="C246">
+        <v>1098</v>
+      </c>
+      <c r="D246">
+        <v>4.75998893674797</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247">
+        <v>5.5</v>
+      </c>
+      <c r="B247">
+        <v>0.112701003615921</v>
+      </c>
+      <c r="C247">
+        <v>1406</v>
+      </c>
+      <c r="D247">
+        <v>5.25297061080461</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248">
+        <v>6</v>
+      </c>
+      <c r="B248">
+        <v>0.112281456042001</v>
+      </c>
+      <c r="C248">
+        <v>1578</v>
+      </c>
+      <c r="D248">
+        <v>5.7433060626392</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249">
+        <v>6.5</v>
+      </c>
+      <c r="B249">
+        <v>0.11165660861935</v>
+      </c>
+      <c r="C249">
+        <v>2018</v>
+      </c>
+      <c r="D249">
+        <v>6.24308779578354</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250">
+        <v>7</v>
+      </c>
+      <c r="B250">
+        <v>0.111015446872206</v>
+      </c>
+      <c r="C250">
+        <v>2342</v>
+      </c>
+      <c r="D250">
+        <v>6.75452277955052</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251">
+        <v>7.5</v>
+      </c>
+      <c r="B251">
+        <v>0.110369601933994</v>
+      </c>
+      <c r="C251">
+        <v>2634</v>
+      </c>
+      <c r="D251">
+        <v>7.25880828593797</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252">
+        <v>8</v>
+      </c>
+      <c r="B252">
+        <v>0.109840117054181</v>
+      </c>
+      <c r="C252">
+        <v>2930</v>
+      </c>
+      <c r="D252">
+        <v>7.7481595567505</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253">
+        <v>8.5</v>
+      </c>
+      <c r="B253">
+        <v>0.109369855428849</v>
+      </c>
+      <c r="C253">
+        <v>3402</v>
+      </c>
+      <c r="D253">
+        <v>8.24275983872338</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254">
+        <v>9</v>
+      </c>
+      <c r="B254">
+        <v>0.108855058511665</v>
+      </c>
+      <c r="C254">
+        <v>3926</v>
+      </c>
+      <c r="D254">
+        <v>8.74722614715433</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255">
+        <v>9.5</v>
+      </c>
+      <c r="B255">
+        <v>0.108377162470149</v>
+      </c>
+      <c r="C255">
+        <v>4266</v>
+      </c>
+      <c r="D255">
+        <v>9.24875254641385</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256">
+        <v>10</v>
+      </c>
+      <c r="B256">
+        <v>0.107884227599452</v>
+      </c>
+      <c r="C256">
+        <v>4730</v>
+      </c>
+      <c r="D256">
+        <v>9.74564847205822</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257">
+        <v>10.5</v>
+      </c>
+      <c r="B257">
+        <v>0.107512001549916</v>
+      </c>
+      <c r="C257">
+        <v>5510</v>
+      </c>
+      <c r="D257">
+        <v>10.2542063522575</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258">
+        <v>11</v>
+      </c>
+      <c r="B258">
+        <v>0.107187119545331</v>
+      </c>
+      <c r="C258">
+        <v>5562</v>
+      </c>
+      <c r="D258">
+        <v>10.7542478228895</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259">
+        <v>11.5</v>
+      </c>
+      <c r="B259">
+        <v>0.106939781772179</v>
+      </c>
+      <c r="C259">
+        <v>6410</v>
+      </c>
+      <c r="D259">
+        <v>11.244987895373</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260">
+        <v>12</v>
+      </c>
+      <c r="B260">
+        <v>0.106750793722632</v>
+      </c>
+      <c r="C260">
+        <v>6894</v>
+      </c>
+      <c r="D260">
+        <v>11.7450714339387</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261">
+        <v>12.5</v>
+      </c>
+      <c r="B261">
+        <v>0.106627730406493</v>
+      </c>
+      <c r="C261">
+        <v>7490</v>
+      </c>
+      <c r="D261">
+        <v>12.2441426243554</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262">
+        <v>13</v>
+      </c>
+      <c r="B262">
+        <v>0.106578149700835</v>
+      </c>
+      <c r="C262">
+        <v>8258</v>
+      </c>
+      <c r="D262">
+        <v>12.7444225452559</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263">
+        <v>13.5</v>
+      </c>
+      <c r="B263">
+        <v>0.106575801952007</v>
+      </c>
+      <c r="C263">
+        <v>8994</v>
+      </c>
+      <c r="D263">
+        <v>13.2528519154988</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264">
+        <v>14</v>
+      </c>
+      <c r="B264">
+        <v>0.106539234982793</v>
+      </c>
+      <c r="C264">
+        <v>9446</v>
+      </c>
+      <c r="D264">
+        <v>13.7542803671108</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265">
+        <v>14.5</v>
+      </c>
+      <c r="B265">
+        <v>0.106509646233922</v>
+      </c>
+      <c r="C265">
+        <v>9978</v>
+      </c>
+      <c r="D265">
+        <v>14.2483018118451</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>15</v>
+      </c>
+      <c r="B266">
+        <v>0.106436439852544</v>
+      </c>
+      <c r="C266">
+        <v>11138</v>
+      </c>
+      <c r="D266">
+        <v>14.7478143756516</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>15.5</v>
+      </c>
+      <c r="B267">
+        <v>0.106376687413911</v>
+      </c>
+      <c r="C267">
+        <v>11406</v>
+      </c>
+      <c r="D267">
+        <v>15.2452282287867</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>16</v>
+      </c>
+      <c r="B268">
+        <v>0.106274214454484</v>
+      </c>
+      <c r="C268">
+        <v>12575</v>
+      </c>
+      <c r="D268">
+        <v>15.7433814113418</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>16.5</v>
+      </c>
+      <c r="B269">
+        <v>0.106083931691323</v>
+      </c>
+      <c r="C269">
+        <v>12848</v>
+      </c>
+      <c r="D269">
+        <v>16.2480191911098</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270">
+        <v>17</v>
+      </c>
+      <c r="B270">
+        <v>0.10580360134245</v>
+      </c>
+      <c r="C270">
+        <v>12060</v>
+      </c>
+      <c r="D270">
+        <v>16.7498118527173</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271">
+        <v>17.5</v>
+      </c>
+      <c r="B271">
+        <v>0.105583477892822</v>
+      </c>
+      <c r="C271">
+        <v>11804</v>
+      </c>
+      <c r="D271">
+        <v>17.2477889982035</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272">
+        <v>18</v>
+      </c>
+      <c r="B272">
+        <v>0.105391866674264</v>
+      </c>
+      <c r="C272">
+        <v>11016</v>
+      </c>
+      <c r="D272">
+        <v>17.7466461218484</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273">
+        <v>18.5</v>
+      </c>
+      <c r="B273">
+        <v>0.105191120611173</v>
+      </c>
+      <c r="C273">
+        <v>10700</v>
+      </c>
+      <c r="D273">
+        <v>18.2476461964778</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274">
+        <v>19</v>
+      </c>
+      <c r="B274">
+        <v>0.105072046509039</v>
+      </c>
+      <c r="C274">
+        <v>9756</v>
+      </c>
+      <c r="D274">
+        <v>18.7461608461768</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275">
+        <v>19.5</v>
+      </c>
+      <c r="B275">
+        <v>0.104991775539163</v>
+      </c>
+      <c r="C275">
+        <v>9224</v>
+      </c>
+      <c r="D275">
+        <v>19.2443623593903</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276">
+        <v>20</v>
+      </c>
+      <c r="B276">
+        <v>0.104910080144793</v>
+      </c>
+      <c r="C276">
+        <v>8408</v>
+      </c>
+      <c r="D276">
+        <v>19.7427539394596</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277">
+        <v>20.5</v>
+      </c>
+      <c r="B277">
+        <v>0.10490840414296</v>
+      </c>
+      <c r="C277">
+        <v>7452</v>
+      </c>
+      <c r="D277">
+        <v>20.2349524648069</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278">
+        <v>21</v>
+      </c>
+      <c r="B278">
+        <v>0.104869144613093</v>
+      </c>
+      <c r="C278">
+        <v>7040</v>
+      </c>
+      <c r="D278">
+        <v>20.7366941177926</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279">
+        <v>21.5</v>
+      </c>
+      <c r="B279">
+        <v>0.104794690371379</v>
+      </c>
+      <c r="C279">
+        <v>5820</v>
+      </c>
+      <c r="D279">
+        <v>21.2419860619221</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280">
+        <v>22</v>
+      </c>
+      <c r="B280">
+        <v>0.10464852911527</v>
+      </c>
+      <c r="C280">
+        <v>4880</v>
+      </c>
+      <c r="D280">
+        <v>21.7372039907627</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281">
+        <v>22.5</v>
+      </c>
+      <c r="B281">
+        <v>0.104403003444517</v>
+      </c>
+      <c r="C281">
+        <v>3936</v>
+      </c>
+      <c r="D281">
+        <v>22.2302479362391</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282">
+        <v>23</v>
+      </c>
+      <c r="B282">
+        <v>0.104012087688084</v>
+      </c>
+      <c r="C282">
+        <v>2999</v>
+      </c>
+      <c r="D282">
+        <v>22.7334385317465</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283">
+        <v>23.5</v>
+      </c>
+      <c r="B283">
+        <v>0.103678978036303</v>
+      </c>
+      <c r="C283">
+        <v>2180</v>
+      </c>
+      <c r="D283">
+        <v>23.2369587045059</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284">
+        <v>24</v>
+      </c>
+      <c r="B284">
+        <v>0.103329594930013</v>
+      </c>
+      <c r="C284">
+        <v>1620</v>
+      </c>
+      <c r="D284">
+        <v>23.7279225769148</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285">
+        <v>24.5</v>
+      </c>
+      <c r="B285">
+        <v>0.10257568106746</v>
+      </c>
+      <c r="C285">
+        <v>1208</v>
+      </c>
+      <c r="D285">
+        <v>24.2151258882127</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286">
+        <v>25</v>
+      </c>
+      <c r="B286">
+        <v>0.101733618734242</v>
+      </c>
+      <c r="C286">
+        <v>942</v>
+      </c>
+      <c r="D286">
+        <v>24.7383759194601</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287">
+        <v>25.5</v>
+      </c>
+      <c r="B287">
+        <v>0.10091895273287</v>
+      </c>
+      <c r="C287">
+        <v>584</v>
+      </c>
+      <c r="D287">
+        <v>25.2823739766508</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288">
+        <v>26</v>
+      </c>
+      <c r="B288">
+        <v>0.100546098091233</v>
+      </c>
+      <c r="C288">
+        <v>284</v>
+      </c>
+      <c r="D288">
+        <v>25.7666230311241</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289">
+        <v>26.5</v>
+      </c>
+      <c r="B289">
+        <v>0.100294788678487</v>
+      </c>
+      <c r="C289">
+        <v>192</v>
+      </c>
+      <c r="D289">
+        <v>26.1687296580041</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290">
+        <v>27</v>
+      </c>
+      <c r="B290">
+        <v>0.099817862877479</v>
+      </c>
+      <c r="C290">
+        <v>104</v>
+      </c>
+      <c r="D290">
+        <v>26.6774814912972</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291">
+        <v>27.5</v>
+      </c>
+      <c r="B291">
+        <v>0.0997238159179688</v>
+      </c>
+      <c r="C291">
+        <v>24</v>
+      </c>
+      <c r="D291">
+        <v>27.2129968013123</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292">
+        <v>28</v>
+      </c>
+      <c r="B292">
+        <v>0.0999832153320312</v>
+      </c>
+      <c r="C292">
+        <v>1</v>
+      </c>
+      <c r="D292">
+        <v>27.712812921102</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">x displacement (um)</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294">
+        <v>0</v>
+      </c>
+      <c r="B294">
+        <v>0.326263427734375</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295">
+        <v>0.5</v>
+      </c>
+      <c r="B295">
+        <v>0.256847381591797</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296">
+        <v>1</v>
+      </c>
+      <c r="B296">
+        <v>0.206550598144531</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297">
+        <v>1.5</v>
+      </c>
+      <c r="B297">
+        <v>0.169914245605469</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298">
+        <v>2</v>
+      </c>
+      <c r="B298">
+        <v>0.144107818603516</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299">
+        <v>2.5</v>
+      </c>
+      <c r="B299">
+        <v>0.127117156982422</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300">
+        <v>3</v>
+      </c>
+      <c r="B300">
+        <v>0.117473602294922</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301">
+        <v>3.5</v>
+      </c>
+      <c r="B301">
+        <v>0.112770080566406</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302">
+        <v>4</v>
+      </c>
+      <c r="B302">
+        <v>0.111461639404297</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303">
+        <v>4.5</v>
+      </c>
+      <c r="B303">
+        <v>0.1104736328125</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304">
+        <v>5</v>
+      </c>
+      <c r="B304">
+        <v>0.110252380371094</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305">
+        <v>5.5</v>
+      </c>
+      <c r="B305">
+        <v>0.109775543212891</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306">
+        <v>6</v>
+      </c>
+      <c r="B306">
+        <v>0.109737396240234</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307">
+        <v>6.5</v>
+      </c>
+      <c r="B307">
+        <v>0.109592437744141</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308">
+        <v>7</v>
+      </c>
+      <c r="B308">
+        <v>0.110126495361328</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309">
+        <v>7.5</v>
+      </c>
+      <c r="B309">
+        <v>0.11090087890625</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310">
+        <v>8</v>
+      </c>
+      <c r="B310">
+        <v>0.111419677734375</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311">
+        <v>8.5</v>
+      </c>
+      <c r="B311">
+        <v>0.111442565917969</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312">
+        <v>9</v>
+      </c>
+      <c r="B312">
+        <v>0.110782623291016</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313">
+        <v>9.5</v>
+      </c>
+      <c r="B313">
+        <v>0.11029052734375</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314">
+        <v>10</v>
+      </c>
+      <c r="B314">
+        <v>0.110233306884766</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315">
+        <v>10.5</v>
+      </c>
+      <c r="B315">
+        <v>0.110435485839844</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316">
+        <v>11</v>
+      </c>
+      <c r="B316">
+        <v>0.111186981201172</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317">
+        <v>11.5</v>
+      </c>
+      <c r="B317">
+        <v>0.112361907958984</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318">
+        <v>12</v>
+      </c>
+      <c r="B318">
+        <v>0.113613128662109</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319">
+        <v>12.5</v>
+      </c>
+      <c r="B319">
+        <v>0.115341186523438</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320">
+        <v>13</v>
+      </c>
+      <c r="B320">
+        <v>0.116401672363281</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321">
+        <v>13.5</v>
+      </c>
+      <c r="B321">
+        <v>0.117565155029297</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322">
+        <v>14</v>
+      </c>
+      <c r="B322">
+        <v>0.118312835693359</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323">
+        <v>14.5</v>
+      </c>
+      <c r="B323">
+        <v>0.118522644042969</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324">
+        <v>15</v>
+      </c>
+      <c r="B324">
+        <v>0.118881225585938</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325">
+        <v>15.5</v>
+      </c>
+      <c r="B325">
+        <v>0.118938446044922</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326">
+        <v>16</v>
+      </c>
+      <c r="B326">
+        <v>0.119094848632812</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">y displacement (um)</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328">
+        <v>0</v>
+      </c>
+      <c r="B328">
+        <v>0.326263427734375</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329">
+        <v>0.5</v>
+      </c>
+      <c r="B329">
+        <v>0.257678985595703</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330">
+        <v>1</v>
+      </c>
+      <c r="B330">
+        <v>0.207683563232422</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331">
+        <v>1.5</v>
+      </c>
+      <c r="B331">
+        <v>0.170978546142578</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332">
+        <v>2</v>
+      </c>
+      <c r="B332">
+        <v>0.145095825195312</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333">
+        <v>2.5</v>
+      </c>
+      <c r="B333">
+        <v>0.127677917480469</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334">
+        <v>3</v>
+      </c>
+      <c r="B334">
+        <v>0.117362976074219</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335">
+        <v>3.5</v>
+      </c>
+      <c r="B335">
+        <v>0.112026214599609</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336">
+        <v>4</v>
+      </c>
+      <c r="B336">
+        <v>0.110721588134766</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337">
+        <v>4.5</v>
+      </c>
+      <c r="B337">
+        <v>0.11090087890625</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338">
+        <v>5</v>
+      </c>
+      <c r="B338">
+        <v>0.111915588378906</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339">
+        <v>5.5</v>
+      </c>
+      <c r="B339">
+        <v>0.113056182861328</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340">
+        <v>6</v>
+      </c>
+      <c r="B340">
+        <v>0.113636016845703</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341">
+        <v>6.5</v>
+      </c>
+      <c r="B341">
+        <v>0.113327026367188</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342">
+        <v>7</v>
+      </c>
+      <c r="B342">
+        <v>0.112030029296875</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343">
+        <v>7.5</v>
+      </c>
+      <c r="B343">
+        <v>0.110481262207031</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344">
+        <v>8</v>
+      </c>
+      <c r="B344">
+        <v>0.109516143798828</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345">
+        <v>8.5</v>
+      </c>
+      <c r="B345">
+        <v>0.108741760253906</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346">
+        <v>9</v>
+      </c>
+      <c r="B346">
+        <v>0.107933044433594</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347">
+        <v>9.5</v>
+      </c>
+      <c r="B347">
+        <v>0.107715606689453</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348">
+        <v>10</v>
+      </c>
+      <c r="B348">
+        <v>0.107509613037109</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349">
+        <v>10.5</v>
+      </c>
+      <c r="B349">
+        <v>0.107147216796875</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350">
+        <v>11</v>
+      </c>
+      <c r="B350">
+        <v>0.107013702392578</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351">
+        <v>11.5</v>
+      </c>
+      <c r="B351">
+        <v>0.106876373291016</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352">
+        <v>12</v>
+      </c>
+      <c r="B352">
+        <v>0.106807708740234</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353">
+        <v>12.5</v>
+      </c>
+      <c r="B353">
+        <v>0.106918334960938</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354">
+        <v>13</v>
+      </c>
+      <c r="B354">
+        <v>0.106983184814453</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355">
+        <v>13.5</v>
+      </c>
+      <c r="B355">
+        <v>0.10693359375</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356">
+        <v>14</v>
+      </c>
+      <c r="B356">
+        <v>0.106033325195312</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357">
+        <v>14.5</v>
+      </c>
+      <c r="B357">
+        <v>0.104663848876953</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358">
+        <v>15</v>
+      </c>
+      <c r="B358">
+        <v>0.103435516357422</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359">
+        <v>15.5</v>
+      </c>
+      <c r="B359">
+        <v>0.102313995361328</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360">
+        <v>16</v>
+      </c>
+      <c r="B360">
+        <v>0.101875305175781</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">z displacement (um)</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pore-pore probability</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362">
+        <v>0</v>
+      </c>
+      <c r="B362">
+        <v>0.326263427734375</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363">
+        <v>0.5</v>
+      </c>
+      <c r="B363">
+        <v>0.263381958007812</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364">
+        <v>1</v>
+      </c>
+      <c r="B364">
+        <v>0.216205596923828</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365">
+        <v>1.5</v>
+      </c>
+      <c r="B365">
+        <v>0.180618286132812</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366">
+        <v>2</v>
+      </c>
+      <c r="B366">
+        <v>0.154586791992188</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367">
+        <v>2.5</v>
+      </c>
+      <c r="B367">
+        <v>0.136222839355469</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368">
+        <v>3</v>
+      </c>
+      <c r="B368">
+        <v>0.123954772949219</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369">
+        <v>3.5</v>
+      </c>
+      <c r="B369">
+        <v>0.116958618164062</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370">
+        <v>4</v>
+      </c>
+      <c r="B370">
+        <v>0.113174438476562</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371">
+        <v>4.5</v>
+      </c>
+      <c r="B371">
+        <v>0.111766815185547</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372">
+        <v>5</v>
+      </c>
+      <c r="B372">
+        <v>0.111480712890625</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373">
+        <v>5.5</v>
+      </c>
+      <c r="B373">
+        <v>0.111309051513672</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374">
+        <v>6</v>
+      </c>
+      <c r="B374">
+        <v>0.110385894775391</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375">
+        <v>6.5</v>
+      </c>
+      <c r="B375">
+        <v>0.108997344970703</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376">
+        <v>7</v>
+      </c>
+      <c r="B376">
+        <v>0.107509613037109</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377">
+        <v>7.5</v>
+      </c>
+      <c r="B377">
+        <v>0.106727600097656</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378">
+        <v>8</v>
+      </c>
+      <c r="B378">
+        <v>0.106796264648437</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379">
+        <v>8.5</v>
+      </c>
+      <c r="B379">
+        <v>0.106990814208984</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380">
+        <v>9</v>
+      </c>
+      <c r="B380">
+        <v>0.107315063476562</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381">
+        <v>9.5</v>
+      </c>
+      <c r="B381">
+        <v>0.107463836669922</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382">
+        <v>10</v>
+      </c>
+      <c r="B382">
+        <v>0.107601165771484</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383">
+        <v>10.5</v>
+      </c>
+      <c r="B383">
+        <v>0.108123779296875</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384">
+        <v>11</v>
+      </c>
+      <c r="B384">
+        <v>0.108890533447266</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385">
+        <v>11.5</v>
+      </c>
+      <c r="B385">
+        <v>0.109382629394531</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386">
+        <v>12</v>
+      </c>
+      <c r="B386">
+        <v>0.109504699707031</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387">
+        <v>12.5</v>
+      </c>
+      <c r="B387">
+        <v>0.109115600585937</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388">
+        <v>13</v>
+      </c>
+      <c r="B388">
+        <v>0.109104156494141</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389">
+        <v>13.5</v>
+      </c>
+      <c r="B389">
+        <v>0.109298706054688</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390">
+        <v>14</v>
+      </c>
+      <c r="B390">
+        <v>0.110271453857422</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391">
+        <v>14.5</v>
+      </c>
+      <c r="B391">
+        <v>0.111423492431641</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392">
+        <v>15</v>
+      </c>
+      <c r="B392">
+        <v>0.112682342529297</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393">
+        <v>15.5</v>
+      </c>
+      <c r="B393">
+        <v>0.113227844238281</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394">
+        <v>16</v>
+      </c>
+      <c r="B394">
+        <v>0.113624572753906</v>
+      </c>
+    </row>
   </sheetData>
 </worksheet>
 </file>